--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/CONNECTICUT_2017.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2017/CONNECTICUT_2017.xlsx
@@ -2346,7 +2346,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C111">
@@ -6162,7 +6162,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C323">
@@ -6414,7 +6414,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C337">
